--- a/Capstone-Project-main/Nopcommerce_ManualTestCases.xlsx
+++ b/Capstone-Project-main/Nopcommerce_ManualTestCases.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ponug\Downloads\Capstone-Project-main\Capstone-Project-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ponug\Desktop\wipro_training\Capstone-Project-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8605B278-3C62-419E-B607-5E3165C7171A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5E6506-5758-474D-9542-5D4C122B90A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="148">
   <si>
     <t>Test case ID</t>
   </si>
@@ -85,9 +85,6 @@
   </si>
   <si>
     <t>Login</t>
-  </si>
-  <si>
-    <t>Anurag Das</t>
   </si>
   <si>
     <t>User is on Login Page</t>
@@ -209,9 +206,6 @@
     <t>User on Registration page</t>
   </si>
   <si>
-    <t>Firstname=Anurag, Lastname=Das, Email=unique@time.com, Password=Anurag@0102</t>
-  </si>
-  <si>
     <t>Fill registration form with valid data, submit</t>
   </si>
   <si>
@@ -265,9 +259,6 @@
     <t>Register with invalid email</t>
   </si>
   <si>
-    <t>Email=anurag (invalid), Password=Pass1234</t>
-  </si>
-  <si>
     <t>Fill form with invalid email, submit</t>
   </si>
   <si>
@@ -465,9 +456,6 @@
     <t>User logged in, product in cart</t>
   </si>
   <si>
-    <t>FirstName=John, LastName=Doe, Email=john.doe@example.com, Address=123 Main St, Phone=9876543210</t>
-  </si>
-  <si>
     <t>Add product to cart, proceed to checkout, fill form, confirm</t>
   </si>
   <si>
@@ -537,67 +525,76 @@
     <t>User logged in + Items in cart</t>
   </si>
   <si>
+    <t>1. Click Checkout 2. Fill info 3. Continue 4. Finish</t>
+  </si>
+  <si>
+    <t>Order confirmation displayed</t>
+  </si>
+  <si>
+    <t>TC_CHECKOUT_005</t>
+  </si>
+  <si>
+    <t>Cancel checkout (Info Page)</t>
+  </si>
+  <si>
+    <t>1. Click Checkout 2. Cancel</t>
+  </si>
+  <si>
+    <t>Redirected to cart page</t>
+  </si>
+  <si>
+    <t>TC_CHECKOUT_006</t>
+  </si>
+  <si>
+    <t>Cancel checkout (Overview Page)</t>
+  </si>
+  <si>
+    <t>1. Click Checkout 2. Fill info 3. Continue 4. Cancel</t>
+  </si>
+  <si>
+    <t>Redirected to products page</t>
+  </si>
+  <si>
+    <t>TC_CHECKOUT_007</t>
+  </si>
+  <si>
+    <t>Verify order summary</t>
+  </si>
+  <si>
+    <t>Items in cart</t>
+  </si>
+  <si>
+    <t>1. Click Checkout 2. Fill info 3. Continue</t>
+  </si>
+  <si>
+    <t>Selected items and total price displayed</t>
+  </si>
+  <si>
+    <t>TC_CHECKOUT_008</t>
+  </si>
+  <si>
+    <t>Verify Finish button completes order</t>
+  </si>
+  <si>
+    <t>Order completion page displayed</t>
+  </si>
+  <si>
+    <t>Venkata Ramireddy</t>
+  </si>
+  <si>
+    <t>Firstname=venkat, Lastname=ram, Email=unique@time.com, Password=venkat@0102</t>
+  </si>
+  <si>
+    <t>Email=ram(invalid), Password=Pass1234</t>
+  </si>
+  <si>
+    <t>FirstName=ram, LastName=reddy, Email=venkat.ram@example.com, Address=123 Main St, Phone=123456789</t>
+  </si>
+  <si>
     <t>Valid checkout info
-First name = Anurag 
-Last Name = Das
+First name = venkat
+Last Name = ram
 Postal Code = 12345</t>
-  </si>
-  <si>
-    <t>1. Click Checkout 2. Fill info 3. Continue 4. Finish</t>
-  </si>
-  <si>
-    <t>Order confirmation displayed</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_005</t>
-  </si>
-  <si>
-    <t>Cancel checkout (Info Page)</t>
-  </si>
-  <si>
-    <t>1. Click Checkout 2. Cancel</t>
-  </si>
-  <si>
-    <t>Redirected to cart page</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_006</t>
-  </si>
-  <si>
-    <t>Cancel checkout (Overview Page)</t>
-  </si>
-  <si>
-    <t>1. Click Checkout 2. Fill info 3. Continue 4. Cancel</t>
-  </si>
-  <si>
-    <t>Redirected to products page</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_007</t>
-  </si>
-  <si>
-    <t>Verify order summary</t>
-  </si>
-  <si>
-    <t>Items in cart</t>
-  </si>
-  <si>
-    <t>1. Click Checkout 2. Fill info 3. Continue</t>
-  </si>
-  <si>
-    <t>Selected items and total price displayed</t>
-  </si>
-  <si>
-    <t>TC_CHECKOUT_008</t>
-  </si>
-  <si>
-    <t>Verify Finish button completes order</t>
-  </si>
-  <si>
-    <t>Order completion page displayed</t>
-  </si>
-  <si>
-    <t>Venkata Ramireddy</t>
   </si>
 </sst>
 </file>
@@ -970,10 +967,10 @@
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
     <col min="2" max="2" width="25.77734375" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="4" width="16.109375" customWidth="1"/>
+    <col min="4" max="4" width="32.21875" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
     <col min="6" max="6" width="23.109375" customWidth="1"/>
-    <col min="7" max="7" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="40.21875" customWidth="1"/>
     <col min="8" max="8" width="37.21875" customWidth="1"/>
     <col min="9" max="9" width="50.21875" customWidth="1"/>
     <col min="10" max="10" width="21.21875" customWidth="1"/>
@@ -1045,1076 +1042,1076 @@
         <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E2" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="J2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P2" s="5"/>
     </row>
     <row r="3" spans="1:16" ht="43.2">
       <c r="A3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="G3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="J3" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="N3" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P3" s="6"/>
     </row>
     <row r="4" spans="1:16" ht="57.6">
       <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="G4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="J4" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="N4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="28.8">
       <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="I5" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="J5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="N5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="14.4" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="J6" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="28.8">
       <c r="A7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E7" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E8" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E7" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" ht="28.8">
-      <c r="A8" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E8" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:16" ht="28.8">
       <c r="A9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E9" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>67</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:16" ht="14.4" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E10" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="J10" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:16" ht="28.8">
       <c r="A11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E11" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E11" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="J11" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="28.8">
       <c r="A12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E12" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="J12" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M12" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="28.8">
       <c r="A13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E13" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="14.4" customHeight="1">
       <c r="A14" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E14" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="J14" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="28.8">
       <c r="A15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="J15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="43.2">
+      <c r="A16" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="B16" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="J15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E16" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" ht="72">
-      <c r="A16" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E16" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="N16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="28.8">
       <c r="A17" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E17" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E17" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>114</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:15" ht="28.8">
       <c r="A18" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E18" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="J18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="M18" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:15" ht="72">
       <c r="A19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E19" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="J19" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:15" ht="57.6">
       <c r="A20" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E20" s="3">
+        <v>45902</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E20" s="3">
-        <v>45902</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="J20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K20" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L20" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M20" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:15" ht="28.8">
       <c r="A21" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E21" s="3">
         <v>45902</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:15" ht="28.8">
       <c r="A22" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E22" s="3">
         <v>45902</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:15" ht="28.8">
       <c r="A23" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E23" s="3">
         <v>45902</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L23" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="57.6">
       <c r="A24" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E24" s="3">
         <v>45902</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="M24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2122,10 +2119,10 @@
     <hyperlink ref="G2" r:id="rId1" tooltip="mailto:demo.123@gmail.com" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="G3" r:id="rId2" tooltip="mailto:demo.123@gmail.com" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="G4" r:id="rId3" tooltip="mailto:unregistered@example.com" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="G6" r:id="rId4" tooltip="mailto:unique@time.com" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="G6" r:id="rId4" tooltip="mailto:unique@time.com" display="Firstname=Anurag, Lastname=Das, Email=unique@time.com, Password=Anurag@0102" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="G7" r:id="rId5" tooltip="mailto:existinguser@mail.com" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
     <hyperlink ref="G9" r:id="rId6" tooltip="mailto:unique@time.com" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="G16" r:id="rId7" tooltip="mailto:john.doe@example.com" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="G16" r:id="rId7" tooltip="mailto:john.doe@example.com" display="FirstName=John, LastName=Doe, Email=john.doe@example.com, Address=123 Main St, Phone=9876543210" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
